--- a/psychologist_forms/017_personality_research_form--psychologist_forms.xlsx
+++ b/psychologist_forms/017_personality_research_form--psychologist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'personality'}</t>
+          <t>personality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Personality'}</t>
+          <t>Personality</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'cognitive'}</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Cognitive'}</t>
+          <t>Cognitive</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'emotional'}</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Emotional'}</t>
+          <t>Emotional</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
